--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/ba-modeling-hard.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/ba-modeling-hard.xlsx
@@ -460,19 +460,19 @@
         <v>Vì "In biên lai" là quan hệ `&lt;&lt;extend&gt;&gt;` (tùy chọn), lỗi không in được biên lai không ảnh hưởng đến việc hoàn thành Use Case chính "Rút tiền". Ngược lại, nếu lỗi ở Use Case include "Xác thực mã PIN", giao dịch sẽ thất bại ngay lập tức.</v>
       </c>
       <c r="F2" t="str">
+        <v>Khách hàng vẫn rút được tiền bình thường nhưng hệ thống sẽ bỏ qua bước in biên lai (không thực hiện Use Case mở rộng)</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Hệ thống báo lỗi và không cho khách hàng nhập mã PIN ngay từ đầu vì thiếu điều kiện tiên quyết</v>
+      </c>
+      <c r="H2" t="str">
         <v>Giao dịch rút tiền bị hủy bỏ hoàn toàn vì không thể in được biên lai — hệ thống dừng hoạt động</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Khách hàng vẫn rút được tiền bình thường nhưng hệ thống sẽ bỏ qua bước in biên lai (không thực hiện Use Case mở rộng)</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Hệ thống báo lỗi và không cho khách hàng nhập mã PIN ngay từ đầu vì thiếu điều kiện tiên quyết</v>
       </c>
       <c r="I2" t="str">
         <v>Hệ thống tự động in biên lai ra màn hình điện tử thay vì in giấy vật lý</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +492,19 @@
         <v>Khi đặc tả quan hệ `&lt;&lt;extend&gt;&gt;`, tài liệu Use Case Specification của Use Case gốc cần chỉ rõ Extension Point (Vị trí mở rộng trong luồng) và điều kiện cụ thể để kích hoạt Use Case mở rộng.</v>
       </c>
       <c r="F3" t="str">
+        <v>Đặc tả "Đăng nhập sai 3 lần" thành một Exception Flow (luồng ngoại lệ) trong tài liệu Đăng nhập, chỉ định rõ Extension Point và điều kiện kích hoạt luồng mở rộng này</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Tạo một Use Case hoàn toàn độc lập và không kết nối gì với Use Case Đăng nhập chính</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Yêu cầu Dev tự viết logic này trong code, BA không cần đưa vào tài liệu đặc tả</v>
+      </c>
+      <c r="I3" t="str">
         <v>Viết luồng đăng nhập sai thành một bước trong Basic Flow của Use Case Đăng nhập</v>
       </c>
-      <c r="G3" t="str">
-        <v>Đặc tả "Đăng nhập sai 3 lần" thành một Exception Flow (luồng ngoại lệ) trong tài liệu Đăng nhập, chỉ định rõ Extension Point và điều kiện kích hoạt luồng mở rộng này</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Tạo một Use Case hoàn toàn độc lập và không kết nối gì với Use Case Đăng nhập chính</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Yêu cầu Dev tự viết logic này trong code, BA không cần đưa vào tài liệu đặc tả</v>
-      </c>
       <c r="J3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -524,19 +524,19 @@
         <v>Nếu phần mềm đúng SRS nhưng sai thực tế, tức là SRS đã bị lỗi thời hoặc BA khơi gợi yêu cầu sai (thiếu Validation động). BA cần xử lý theo quy trình quản lý thay đổi (CR) để cập nhật hệ thống.</v>
       </c>
       <c r="F4" t="str">
+        <v>Lỗi ở giai đoạn kiểm thử (Testing) — QA không phát hiện ra quy trình nghiệp vụ bị thay đổi</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Lỗi ở phía khách hàng — Khách hàng phải tự thay đổi quy trình làm việc của mình theo phần mềm</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Lỗi ở giai đoạn khơi gợi và xác thực yêu cầu (Elicitation &amp; Validation) — BA đã validate tài liệu SRS tĩnh mà không kiểm tra quy trình nghiệp vụ động thực tế. Giải pháp: Lập biên bản ghi nhận thay đổi, phân tích tác động và đề xuất quy trình nâng cấp hệ thống (CR)</v>
+      </c>
+      <c r="I4" t="str">
         <v>Lỗi ở giai đoạn lập trình (Construction) — Dev code sai logic nghiệp vụ thực tế</v>
       </c>
-      <c r="G4" t="str">
-        <v>Lỗi ở giai đoạn khơi gợi và xác thực yêu cầu (Elicitation &amp; Validation) — BA đã validate tài liệu SRS tĩnh mà không kiểm tra quy trình nghiệp vụ động thực tế. Giải pháp: Lập biên bản ghi nhận thay đổi, phân tích tác động và đề xuất quy trình nâng cấp hệ thống (CR)</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Lỗi ở giai đoạn kiểm thử (Testing) — QA không phát hiện ra quy trình nghiệp vụ bị thay đổi</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Lỗi ở phía khách hàng — Khách hàng phải tự thay đổi quy trình làm việc của mình theo phần mềm</v>
-      </c>
       <c r="J4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -556,19 +556,19 @@
         <v>Sơ đồ Use Case sinh ra để khách hàng hiểu được hệ thống làm gì. Việc lạm dụng chi tiết hóa include/extend biến nó thành sơ đồ thiết kế thuật toán kỹ thuật, mất đi tính giao tiếp nghiệp vụ.</v>
       </c>
       <c r="F5" t="str">
+        <v>Vì làm tăng thời gian chạy của cơ sở dữ liệu khi hệ thống vận hành thực tế</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Vì compiler của Java và C# không hỗ trợ biên dịch các sơ đồ có mối quan hệ này</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Vì trình duyệt không thể render được sơ đồ Use Case nếu có quá nhiều đường nét đứt</v>
+      </c>
+      <c r="I5" t="str">
         <v>Vì làm sơ đồ trở nên quá phức tạp, khó đọc đối với khách hàng (Business stakeholders) và dễ dẫn đến tư duy phân rã chức năng kiểu lập trình (Functional Decomposition) thay vì tập trung vào mục tiêu của tác nhân</v>
       </c>
-      <c r="G5" t="str">
-        <v>Vì trình duyệt không thể render được sơ đồ Use Case nếu có quá nhiều đường nét đứt</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Vì làm tăng thời gian chạy của cơ sở dữ liệu khi hệ thống vận hành thực tế</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Vì compiler của Java và C# không hỗ trợ biên dịch các sơ đồ có mối quan hệ này</v>
-      </c>
       <c r="J5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -588,19 +588,19 @@
         <v>Usability đo lường tính dễ dùng. Để test được, nó phải được lượng hóa thông qua thời gian hoàn thành tác vụ (Task completion time), tỷ lệ lỗi của người dùng (Error rate) và thời gian học sử dụng (Learning curve).</v>
       </c>
       <c r="F6" t="str">
+        <v>Tần suất người dùng mở ứng dụng di động tối thiểu 3 lần một ngày</v>
+      </c>
+      <c r="G6" t="str">
         <v>Mức độ hài lòng của người dùng khi đánh giá giao diện trên thang điểm từ 1 đến 5</v>
       </c>
-      <c r="G6" t="str">
+      <c r="H6" t="str">
         <v>Thời gian trung bình một người dùng mới hoàn thành tác vụ cốt lõi không quá 3 phút sau tối đa 15 phút hướng dẫn, và tỷ lệ thực hiện lỗi dưới 5%</v>
       </c>
-      <c r="H6" t="str">
+      <c r="I6" t="str">
         <v>Số lượng màu sắc phối hợp trên một trang web không được vượt quá 3 tông màu chủ đạo</v>
       </c>
-      <c r="I6" t="str">
-        <v>Tần suất người dùng mở ứng dụng di động tối thiểu 3 lần một ngày</v>
-      </c>
       <c r="J6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -620,19 +620,19 @@
         <v>Data Mapping chi tiết (Source Field, Target Field, Type, Rules, Nullability) là bắt buộc để lập trình viên viết code chuyển đổi dữ liệu chính xác, tránh mất mát thông tin hoặc lỗi kiểu dữ liệu ở runtime.</v>
       </c>
       <c r="F7" t="str">
+        <v>Đường truyền mạng internet cáp quang kết nối giữa hai văn phòng công ty</v>
+      </c>
+      <c r="G7" t="str">
         <v>Ánh xạ chi tiết giữa các trường dữ liệu nguồn và đích (Source to Target Field mapping), kiểu dữ liệu, độ dài, quy tắc biến đổi (Transformation rules) và cách xử lý lỗi khi không khớp dữ liệu</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Tên của máy chủ vật lý lưu trữ dữ liệu của cả hai hệ thống</v>
       </c>
       <c r="H7" t="str">
         <v>Danh sách số lượng lập trình viên tham gia viết code tích hợp API của hai bên</v>
       </c>
       <c r="I7" t="str">
-        <v>Đường truyền mạng internet cáp quang kết nối giữa hai văn phòng công ty</v>
+        <v>Tên của máy chủ vật lý lưu trữ dữ liệu của cả hai hệ thống</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -652,19 +652,19 @@
         <v>Sub-flow giúp chia nhỏ luồng cơ bản dài thành các khối logic tuần tự dễ quản lý. Alternative Flow là nhánh rẽ nghiệp vụ tùy chọn dựa trên quyết định/điều kiện cụ thể.</v>
       </c>
       <c r="F8" t="str">
+        <v>Sub-flow chỉ chạy trên mobile; Alternative Flow chỉ chạy trên môi trường desktop web</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Sub-flow luôn kết thúc bằng lỗi hệ thống; Alternative Flow luôn kết thúc thành công</v>
+      </c>
+      <c r="H8" t="str">
         <v>Sub-flow là một phần của luồng cơ bản được tách ra để dễ đọc (vẫn chạy bắt buộc); Alternative Flow là luồng rẽ nhánh tùy chọn dẫn đến kết quả khác</v>
       </c>
-      <c r="G8" t="str">
+      <c r="I8" t="str">
         <v>Sub-flow do dev viết; Alternative Flow do BA viết tài liệu đặc tả</v>
       </c>
-      <c r="H8" t="str">
-        <v>Sub-flow luôn kết thúc bằng lỗi hệ thống; Alternative Flow luôn kết thúc thành công</v>
-      </c>
-      <c r="I8" t="str">
-        <v>Sub-flow chỉ chạy trên mobile; Alternative Flow chỉ chạy trên môi trường desktop web</v>
-      </c>
       <c r="J8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -687,16 +687,16 @@
         <v>Để dev tự quyết định hoàn toàn vì đây là chi tiết kỹ thuật không liên quan đến BA</v>
       </c>
       <c r="G9" t="str">
+        <v>Viết một file SRS duy nhất và yêu cầu tất cả các dịch vụ sử dụng chung một database tập trung</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Yêu cầu khách hàng cung cấp sơ đồ đi dây mạng của hệ thống máy chủ</v>
+      </c>
+      <c r="I9" t="str">
         <v>Đặc tả rõ ràng luồng nghiệp vụ đi qua các service, kiểu giao tiếp (đồng bộ qua REST/gRPC hay bất đồng bộ qua Message Queue như RabbitMQ/Kafka) và cấu trúc dữ liệu trao đổi giữa các dịch vụ</v>
       </c>
-      <c r="H9" t="str">
-        <v>Viết một file SRS duy nhất và yêu cầu tất cả các dịch vụ sử dụng chung một database tập trung</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Yêu cầu khách hàng cung cấp sơ đồ đi dây mạng của hệ thống máy chủ</v>
-      </c>
       <c r="J9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -716,19 +716,19 @@
         <v>Độ sẵn sàng 99.9% (thường gọi là 3 con 9) tương đương với tối đa 8.76 giờ downtime ngoài ý muốn mỗi năm. QA cần dùng công cụ giám sát thời gian hoạt động (uptime) dài hạn để xác thực.</v>
       </c>
       <c r="F10" t="str">
+        <v>Kiểm tra xem hệ thống có tự động re-render giao diện khi người dùng nhấn F5 liên tục hay không</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Chạy thử hệ thống liên tục trong vòng 5 phút, nếu không sập là đạt yêu cầu</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Đo lường dung lượng bộ nhớ RAM của server không vượt quá 90% dưới tải cao</v>
+      </c>
+      <c r="I10" t="str">
         <v>Đo lường tổng thời gian hệ thống bị dừng hoạt động ngoài kế hoạch (Unplanned downtime) không được vượt quá 8.76 giờ trong vòng một năm hoạt động liên tục</v>
       </c>
-      <c r="G10" t="str">
-        <v>Kiểm tra xem hệ thống có tự động re-render giao diện khi người dùng nhấn F5 liên tục hay không</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Chạy thử hệ thống liên tục trong vòng 5 phút, nếu không sập là đạt yêu cầu</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Đo lường dung lượng bộ nhớ RAM của server không vượt quá 90% dưới tải cao</v>
-      </c>
       <c r="J10">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -748,19 +748,19 @@
         <v>Spider Web khiến sơ đồ Use Case mất đi tính trực quan. BA khắc phục bằng cách gom nhóm các Use Case có liên quan vào các Subsystem/Boundary hoặc phân mảnh sơ đồ thành nhiều view nhỏ hơn.</v>
       </c>
       <c r="F11" t="str">
+        <v>Khi cơ sở dữ liệu có quá nhiều bảng quan hệ nhiều-nhiều không có khóa ngoại</v>
+      </c>
+      <c r="G11" t="str">
         <v>Khi một Actor kết nối trực tiếp đến quá nhiều Use Case hoặc các Use Case kết nối chằng chịt lẫn nhau — Khắc phục: Phân nhóm Use Case thành các gói (Package/Subject), sử dụng quan hệ kế thừa Actor và tinh chỉnh cấu trúc sơ đồ</v>
       </c>
-      <c r="G11" t="str">
+      <c r="H11" t="str">
         <v>Khi lập trình viên viết code có quá nhiều vòng lặp lồng nhau gây đơ trình duyệt</v>
-      </c>
-      <c r="H11" t="str">
-        <v>Khi cơ sở dữ liệu có quá nhiều bảng quan hệ nhiều-nhiều không có khóa ngoại</v>
       </c>
       <c r="I11" t="str">
         <v>Khi hệ thống bị tấn công bởi virus mạng làm tắc nghẽn đường truyền internet</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
